--- a/originales/respuestas/2025/01. Calificadas/bucle p35/Subred Integrada De Servicios De Salud Sur.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p35/Subred Integrada De Servicios De Salud Sur.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TfCf+y9xt4kSFiTRaxP//Tz2jjr/HM/IVDQPtuyaNsE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="w2D26MOcP6F4xqTMBIauGWsQF02eTgg4o8DrlDqyueI="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
   <si>
     <t>Entidad</t>
   </si>
@@ -146,26 +146,14 @@
   </si>
   <si>
     <t>GESTIÓN DE CONOCIMIENTO</t>
-  </si>
-  <si>
-    <t>LAS LINEAS DEL</t>
-  </si>
-  <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/LINEAS GESTIÓN DE CONOCIMIENTO.pdf</t>
-  </si>
-  <si>
-    <t>Las lineas del proceso: Gestión del Conocimiento son: 
- 1.</t>
-  </si>
-  <si>
-    <t>Las lineas del proceso: Gestión del Conocimiento son: 
- 1. FTHS - Formación Talento Humano en Salud
- 2.</t>
   </si>
   <si>
     <t>Las lineas del proceso: Gestión del Conocimiento son: 
  1. FTHS - Formación Talento Humano en Salud
  2. ICT - Innovación, Ciencia y Tecnología</t>
+  </si>
+  <si>
+    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/LINEAS GESTIÓN DE CONOCIMIENTO.pdf</t>
   </si>
 </sst>
 </file>
@@ -844,132 +832,9 @@
       </c>
       <c r="P7" s="4"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P8" s="4"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P9" s="4"/>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P10" s="4"/>
-    </row>
+    <row r="8" ht="14.25" customHeight="1"/>
+    <row r="9" ht="14.25" customHeight="1"/>
+    <row r="10" ht="14.25" customHeight="1"/>
     <row r="11" ht="14.25" customHeight="1"/>
     <row r="12" ht="14.25" customHeight="1"/>
     <row r="13" ht="14.25" customHeight="1"/>
@@ -1957,9 +1822,6 @@
     <row r="995" ht="14.25" customHeight="1"/>
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
